--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -1029,17 +1029,25 @@
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>依頼中</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H10" s="24" t="n"/>
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="27" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="24" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>summer-bunjin-zakurobana.webp</t>
+        </is>
+      </c>
       <c r="M10" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>
@@ -1358,17 +1366,25 @@
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>依頼中</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H17" s="27" t="n"/>
       <c r="I17" s="27" t="n"/>
       <c r="J17" s="27" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
+      <c r="K17" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L17" s="27" t="inlineStr">
+        <is>
+          <t>autumn-bunjin-keika.webp</t>
+        </is>
+      </c>
       <c r="M17" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>
@@ -1930,17 +1946,25 @@
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>依頼中</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H29" s="27" t="n"/>
       <c r="I29" s="27" t="n"/>
       <c r="J29" s="27" t="n"/>
-      <c r="K29" s="27" t="n"/>
-      <c r="L29" s="27" t="n"/>
+      <c r="K29" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L29" s="27" t="inlineStr">
+        <is>
+          <t>winter-morimono-busshukan.webp</t>
+        </is>
+      </c>
       <c r="M29" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>
@@ -1977,17 +2001,25 @@
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>依頼中</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H30" s="27" t="n"/>
       <c r="I30" s="27" t="n"/>
       <c r="J30" s="27" t="n"/>
-      <c r="K30" s="27" t="n"/>
-      <c r="L30" s="27" t="n"/>
+      <c r="K30" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L30" s="27" t="inlineStr">
+        <is>
+          <t>spring-bunjin-botan.webp</t>
+        </is>
+      </c>
       <c r="M30" s="24" t="inlineStr">
         <is>
-          <t>追加項目(元28種リスト外) ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照)</t>
+          <t>追加項目(元28種リスト外) ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>

--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M10" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補で高精度に再切り抜き</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="M17" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補で高精度に再切り抜き</t>
         </is>
       </c>
     </row>
@@ -1946,25 +1946,17 @@
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>切り抜き済</t>
+          <t>依頼中</t>
         </is>
       </c>
       <c r="H29" s="27" t="n"/>
       <c r="I29" s="27" t="n"/>
       <c r="J29" s="27" t="n"/>
-      <c r="K29" s="27" t="inlineStr">
-        <is>
-          <t>AI生成（Canva AI）</t>
-        </is>
-      </c>
-      <c r="L29" s="27" t="inlineStr">
-        <is>
-          <t>winter-morimono-busshukan.webp</t>
-        </is>
-      </c>
+      <c r="K29" s="27" t="n"/>
+      <c r="L29" s="27" t="n"/>
       <c r="M29" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 AI生成したが考証で不採用（アプリ未登録）</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2011,7 @@
       </c>
       <c r="M30" s="24" t="inlineStr">
         <is>
-          <t>追加項目(元28種リスト外) ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち）</t>
+          <t>追加項目(元28種リスト外) ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補で高精度に再切り抜き</t>
         </is>
       </c>
     </row>

--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M10" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補で高精度に再切り抜き</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補からMLセグメンテーション(rembg/isnet)で再切り抜き(最終版)</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="M17" s="27" t="inlineStr">
         <is>
-          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補で高精度に再切り抜き</t>
+          <t>AI生成候補 ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補からMLセグメンテーション(rembg/isnet)で再切り抜き(最終版)</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M30" s="24" t="inlineStr">
         <is>
-          <t>追加項目(元28種リスト外) ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補で高精度に再切り抜き</t>
+          <t>追加項目(元28種リスト外) ／ AI生成プロンプト作成済(AI生成花材_プロンプト集.md参照) ／ 2026-07-15 Canva AIで生成・hana-ar.htmlに登録済（学芸員考証チェック待ち） ／ 2026-07-15 指定候補からMLセグメンテーション(rembg/isnet)で再切り抜き(最終版)</t>
         </is>
       </c>
     </row>

--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -653,17 +653,25 @@
       </c>
       <c r="G2" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H2" s="24" t="n"/>
       <c r="I2" s="27" t="n"/>
       <c r="J2" s="27" t="n"/>
-      <c r="K2" s="24" t="n"/>
-      <c r="L2" s="24" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）暫定</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>spring-bunjin-ume-zanshun.webp</t>
+        </is>
+      </c>
       <c r="M2" s="24" t="inlineStr">
         <is>
-          <t>時期不可なら③で補完 ／ AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>時期不可なら③で補完 ／ AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-07-15 AI生成の暫定素材をhana-ar.htmlに登録（本調達①②の素材が届き次第差し替え・学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>
@@ -700,17 +708,25 @@
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H3" s="24" t="n"/>
       <c r="I3" s="27" t="n"/>
       <c r="J3" s="27" t="n"/>
-      <c r="K3" s="24" t="n"/>
-      <c r="L3" s="24" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）暫定</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>spring-bunjin-kaido.webp</t>
+        </is>
+      </c>
       <c r="M3" s="24" t="inlineStr">
         <is>
-          <t>時期不可なら③で補完 ／ AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>時期不可なら③で補完 ／ AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-07-15 AI生成の暫定素材をhana-ar.htmlに登録（本調達①②の素材が届き次第差し替え・学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>
@@ -747,17 +763,25 @@
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H4" s="24" t="n"/>
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
-      <c r="K4" s="24" t="n"/>
-      <c r="L4" s="24" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）暫定</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t>spring-bunjin-ran.webp</t>
+        </is>
+      </c>
       <c r="M4" s="24" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-07-15 AI生成の暫定素材をhana-ar.htmlに登録（本調達①②の素材が届き次第差し替え・学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>
@@ -794,17 +818,25 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H5" s="24" t="n"/>
       <c r="I5" s="27" t="n"/>
       <c r="J5" s="27" t="n"/>
-      <c r="K5" s="24" t="n"/>
-      <c r="L5" s="24" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）暫定</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="inlineStr">
+        <is>
+          <t>spring-gyo-momo.webp</t>
+        </is>
+      </c>
       <c r="M5" s="24" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-07-15 AI生成の暫定素材をhana-ar.htmlに登録（本調達①②の素材が届き次第差し替え・学芸員考証チェック待ち）</t>
         </is>
       </c>
     </row>

--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -1743,17 +1743,25 @@
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H24" s="27" t="n"/>
       <c r="I24" s="27" t="n"/>
       <c r="J24" s="27" t="n"/>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="27" t="n"/>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）暫定</t>
+        </is>
+      </c>
+      <c r="L24" s="27" t="inlineStr">
+        <is>
+          <t>winter-bunjin-ume-hitoeda.webp</t>
+        </is>
+      </c>
       <c r="M24" s="27" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-07-17 春バッチの梅未採用候補(候補2)を一枝の梅の暫定素材として転用。①本調達素材の確保後に差し替え</t>
         </is>
       </c>
     </row>

--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -1696,17 +1696,25 @@
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H23" s="27" t="n"/>
       <c r="I23" s="27" t="n"/>
       <c r="J23" s="27" t="n"/>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="27" t="n"/>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）暫定</t>
+        </is>
+      </c>
+      <c r="L23" s="27" t="inlineStr">
+        <is>
+          <t>winter-bunjin-suisen.webp</t>
+        </is>
+      </c>
       <c r="M23" s="27" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ ①本調達(撮影)確保後に差替 ／ 2026-08-13 Canva AI暫定採用(候補1)</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1806,25 @@
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H25" s="27" t="n"/>
       <c r="I25" s="27" t="n"/>
       <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）暫定</t>
+        </is>
+      </c>
+      <c r="L25" s="27" t="inlineStr">
+        <is>
+          <t>winter-shin-shouchikubai.webp</t>
+        </is>
+      </c>
       <c r="M25" s="27" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ ①本調達確保後に差替 ／ 2026-08-13 Canva AI暫定採用(松竹梅3種そろい・再生成候補)</t>
         </is>
       </c>
     </row>
@@ -1845,17 +1861,25 @@
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H26" s="27" t="n"/>
       <c r="I26" s="27" t="n"/>
       <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="27" t="n"/>
+      <c r="K26" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L26" s="27" t="inlineStr">
+        <is>
+          <t>winter-so-nanten.webp</t>
+        </is>
+      </c>
       <c r="M26" s="27" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ ②ストック確保後に差替可 ／ 2026-08-13 Canva AI採用(候補2)</t>
         </is>
       </c>
     </row>
@@ -1892,17 +1916,25 @@
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H27" s="27" t="n"/>
       <c r="I27" s="27" t="n"/>
       <c r="J27" s="27" t="n"/>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="27" t="n"/>
+      <c r="K27" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L27" s="27" t="inlineStr">
+        <is>
+          <t>winter-gyo-sancha.webp</t>
+        </is>
+      </c>
       <c r="M27" s="27" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ ②ストック確保後に差替可 ／ 2026-08-13 Canva AI採用(候補2)</t>
         </is>
       </c>
     </row>
@@ -1939,17 +1971,25 @@
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H28" s="27" t="n"/>
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="27" t="n"/>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="27" t="n"/>
+      <c r="K28" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L28" s="27" t="inlineStr">
+        <is>
+          <t>winter-bonsai-suisen.webp</t>
+        </is>
+      </c>
       <c r="M28" s="27" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ ①/②確保後に差替 ／ 2026-08-13 Canva AI採用(候補4・器なし根束ね)</t>
         </is>
       </c>
     </row>

--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -873,17 +873,25 @@
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H6" s="24" t="n"/>
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="27" t="n"/>
-      <c r="K6" s="24" t="n"/>
-      <c r="L6" s="24" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>spring-shin-mokuren.webp</t>
+        </is>
+      </c>
       <c r="M6" s="24" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-08-13 Canva AI採用(候補2・紫木蓮の盃形)</t>
         </is>
       </c>
     </row>
@@ -920,17 +928,25 @@
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H7" s="24" t="n"/>
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="27" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>spring-so-yamabuki.webp</t>
+        </is>
+      </c>
       <c r="M7" s="24" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-08-13 Canva AI採用(候補1)</t>
         </is>
       </c>
     </row>
@@ -967,17 +983,25 @@
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H8" s="24" t="n"/>
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="27" t="n"/>
-      <c r="K8" s="24" t="n"/>
-      <c r="L8" s="24" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>spring-bonsai-bonbai.webp</t>
+        </is>
+      </c>
       <c r="M8" s="24" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-08-13 Canva AI採用(候補3・古木/器なし)</t>
         </is>
       </c>
     </row>

--- a/素材調達管理シート.xlsx
+++ b/素材調達管理シート.xlsx
@@ -1187,17 +1187,25 @@
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>切り抜き済</t>
         </is>
       </c>
       <c r="H12" s="27" t="n"/>
       <c r="I12" s="27" t="n"/>
       <c r="J12" s="27" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="27" t="n"/>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>AI生成（Canva AI）</t>
+        </is>
+      </c>
+      <c r="L12" s="27" t="inlineStr">
+        <is>
+          <t>summer-shin-shoubu.webp</t>
+        </is>
+      </c>
       <c r="M12" s="27" t="inlineStr">
         <is>
-          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照)</t>
+          <t>AI生成プロンプト作成済(参考用／AI生成花材_プロンプト集.md参照) ／ 2026-08-13 Canva AI採用(候補1)</t>
         </is>
       </c>
     </row>
